--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.46937622991946</v>
+        <v>10.63877363736191</v>
       </c>
       <c r="D2" t="n">
-        <v>55.87933428379404</v>
+        <v>9.080391821116532</v>
       </c>
       <c r="E2" t="n">
-        <v>18.63112398412301</v>
+        <v>3.02755764741999</v>
       </c>
       <c r="F2" t="n">
-        <v>18.88843025221966</v>
+        <v>3.069369915985696</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.3166127725308</v>
+        <v>5.738949575536256</v>
       </c>
       <c r="D3" t="n">
-        <v>3.354101966249685</v>
+        <v>0.5450415695155738</v>
       </c>
       <c r="E3" t="n">
-        <v>18.63112398412301</v>
+        <v>3.02755764741999</v>
       </c>
       <c r="F3" t="n">
-        <v>18.88843025221966</v>
+        <v>3.069369915985696</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.48863471856577</v>
+        <v>2.841903141766938</v>
       </c>
       <c r="D4" t="n">
-        <v>16.11827721585885</v>
+        <v>2.619220047577064</v>
       </c>
       <c r="E4" t="n">
-        <v>18.63112398412301</v>
+        <v>3.02755764741999</v>
       </c>
       <c r="F4" t="n">
-        <v>18.88843025221966</v>
+        <v>3.069369915985696</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.00954636380681</v>
+        <v>5.851551284118607</v>
       </c>
       <c r="D5" t="n">
-        <v>36.89706584807561</v>
+        <v>5.995773200312287</v>
       </c>
       <c r="E5" t="n">
-        <v>18.63112398412301</v>
+        <v>3.02755764741999</v>
       </c>
       <c r="F5" t="n">
-        <v>18.88843025221966</v>
+        <v>3.069369915985696</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.41443739145906</v>
+        <v>3.317346076112097</v>
       </c>
       <c r="D6" t="n">
-        <v>9.384039624944316</v>
+        <v>1.524906439053451</v>
       </c>
       <c r="E6" t="n">
-        <v>18.63112398412301</v>
+        <v>3.02755764741999</v>
       </c>
       <c r="F6" t="n">
-        <v>18.88843025221966</v>
+        <v>3.069369915985696</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.360555728649604</v>
+        <v>1.196090305905561</v>
       </c>
       <c r="D7" t="n">
-        <v>6.780870823076063</v>
+        <v>1.10189150874986</v>
       </c>
       <c r="E7" t="n">
-        <v>18.63112398412301</v>
+        <v>3.02755764741999</v>
       </c>
       <c r="F7" t="n">
-        <v>18.88843025221966</v>
+        <v>3.069369915985696</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
